--- a/school_surveys/032_faculty_evaluation_form--school_surveys.xlsx
+++ b/school_surveys/032_faculty_evaluation_form--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>course_satisfaction</t>
+          <t>course_satisfaction_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Course Satisfaction</t>
+          <t>Course Satisfaction 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>overall_satisfaction</t>
+          <t>overall_satisfaction_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Overall Satisfaction</t>
+          <t>Overall Satisfaction 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>course_evaluation</t>
+          <t>course_evaluation_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Course Evaluation</t>
+          <t>Course Evaluation 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,80 +1216,80 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>course_materials_choices</t>
+          <t>student_support_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>support_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Support 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>course_materials_choices</t>
+          <t>student_support_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>support_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>Support 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>student_support_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>support_1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Support 1</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>student_support_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>support_2</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Support 2</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1301,267 +1301,165 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>overall_satisfaction_choices</t>
+          <t>overall_evaluation_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>overall_satisfaction_choices</t>
+          <t>overall_evaluation_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>overall_satisfaction_choices</t>
+          <t>overall_evaluation_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>overall_satisfaction_choices</t>
+          <t>course_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>overall_evaluation_choices</t>
+          <t>course_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>overall_evaluation_choices</t>
+          <t>course_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>overall_evaluation_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>course_satisfaction_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>course_satisfaction_choices</t>
+          <t>overall_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>course_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>course_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>course_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option_5</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Option 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Option 3</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
